--- a/questions.xlsx
+++ b/questions.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30327"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5771B3DA-733F-44EF-B3B3-41B9C2AE6272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F03BA2E-5DEA-4052-802A-A0BF41AD30C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="206">
   <si>
     <t>Fənn</t>
   </si>
@@ -66,59 +66,747 @@
     <t>Qanunvericilik</t>
   </si>
   <si>
-    <t>Konstitusiya</t>
-  </si>
-  <si>
-    <t>Konstitusiya neçənci ildə qəbul edilib?</t>
-  </si>
-  <si>
-    <t>Kim ders edir ki?</t>
-  </si>
-  <si>
-    <t>heckim</t>
-  </si>
-  <si>
-    <t>men</t>
-  </si>
-  <si>
-    <t>kimse</t>
-  </si>
-  <si>
-    <t>hami</t>
-  </si>
-  <si>
-    <t>Belkede yoxdu</t>
-  </si>
-  <si>
-    <t>ne?</t>
-  </si>
-  <si>
-    <t>he</t>
-  </si>
-  <si>
-    <t>kimdi sorusan</t>
-  </si>
-  <si>
-    <t>Bilmirem</t>
-  </si>
-  <si>
-    <t>neyi</t>
-  </si>
-  <si>
-    <t>kimi</t>
+    <t>Azərbaycan Respublikasının Konstitusiyası</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyası qəbul olunub?</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Prezidenti Heydər Əliyevin sədrliyi ilə Azərbaycan Respublikasının yeni Konstitusiya layihəsini hazırlayan komissiya tərəfindən hazırlanmış, 1995-ci il noyabrın 27-də ümumxalq səsverməsində (referendumda) qəbul edilmişdir</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Prezidenti Heydər Əliyevin sədrliyi ilə Azərbaycan Respublikasının yeni Konstitusiya layihəsini hazırlayan komissiya tərəfindən hazırlanmış, 1991-ci il oktyabrın 18-də ümumxalq səsverməsində (referendumda)qəbul edilmişdi</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Prezidenti Heydər Əliyevin sədrliyi ilə Azərbaycan Respublikasının yeni Konstitusiya layihəsini hazırlayan komissiya tərəfindən hazırlanmış, 1995-ci il noyabrın 12-də ümumxalq səsverməsində (referendumda)qəbul edilmişdir</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Prezidenti Heydər Əliyevin sədrliyi ilə Azərbaycan Respublikasının yeni Konstitusiya layihəsini hazırlayan komissiya tərəfindən hazırlanmış, 1995-ci il noyabrın 17-də ümumxalq səsverməsində (referendumda)qəbul edilmişdir</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının konstitusiyası nə zaman qüvvəyə minmişdir?</t>
+  </si>
+  <si>
+    <t>1991-ci il 18 oktyabr</t>
+  </si>
+  <si>
+    <t>1995-ci il 12 noyabr</t>
+  </si>
+  <si>
+    <t>1995-ci il 17 noyabr</t>
+  </si>
+  <si>
+    <t>1995-ci il 27 noyabr</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının konstitusiyasına ilk dəyişikliklər nə zaman olunub?</t>
+  </si>
+  <si>
+    <t>1995-ci il noyabrın 12-də</t>
+  </si>
+  <si>
+    <t>2002-ci il avqustun 24-də</t>
+  </si>
+  <si>
+    <t>2009-cu il martın 18-də</t>
+  </si>
+  <si>
+    <t>2016-cı il sentyabrın 26-da</t>
+  </si>
+  <si>
+    <t>Azərbaycan ümumi və bölünməz vətənidir:</t>
+  </si>
+  <si>
+    <t>Azərbaycanda yaşayan və azərbaycan respublikasının ərazisində qanuni mülkiyyəti olan bütün şəxslərin</t>
+  </si>
+  <si>
+    <t>Cinsindən və milli mənsubiyyətindən aslı olmayaraq azərbaycan respublikasının ərazisində yaşayan azərbaycan dövləti qarşısında öhdəlikləri</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikası ərazisində və ondan kənarda yaşayan doğulduğu ölkənin qanunlarına tabe sayılan bütün vətəndaşların</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının bütün vətəndaşlarının</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının konstitusiyasına ikinci dəyişikliklər nə zaman olunub?</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikası rədd edir:</t>
+  </si>
+  <si>
+    <t>Başqa dövlətlərin müstəqilliyinə qəsd vasitəsi kimi və beynəlxalq münaqişələrin həll üsulu kimi müharibəni</t>
+  </si>
+  <si>
+    <t>Xalqın suverenliyini və dövlətin ərazi bütövlüyünü qorumaq üçün silahlı qüvvələrdən istifadəni</t>
+  </si>
+  <si>
+    <t>Ümumbəşəri dəyərlərə sadiq qalaraq bütün dünya xalqaları ilə dostkuq sülh və əmin amanlıq içində yaşamağ</t>
+  </si>
+  <si>
+    <t>İnsan və vətəndaş hüquq və azadlıqları üçün real təhlükə yarandıqda silah tətbiq edilməsini</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına ikinci əlavə nə zaman olunub?</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına ilk əlavələr nə zaman olunub?</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan xalqı hansı formada öz niyyətlərini bəyan edir?</t>
+  </si>
+  <si>
+    <t>Təntənəli</t>
+  </si>
+  <si>
+    <t>Rəsmi</t>
+  </si>
+  <si>
+    <t>Qeyri rəsmi</t>
+  </si>
+  <si>
+    <t>Hər biri</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan xalqı özünün çoxəsrlik dövlətçilik ənənələrini davam etdirərək, .......... əsas götürərək, .......... arzulayaraq, ............ istəyərək, ......... anlayaraq, suveren hüququndan istifadə edərək, təntənəli surətdə niyyətlərini bəyan edir: 
+1.“Azərbaycan Respublikasının dövlət müstəqilliyi haqqında” Konstitusiya aktında əks olunan prinsipləri 
+2.ədalətin, azadlığın və təhlükəsizliyin bərqərar edilməsini 
+3.bütün cəmiyyətin və hər kəsin firavanlığının təmin edilməsini 
+4.keçmiş, indiki və gələcək nəsillər qarşısında öz məsuliyyətini</t>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+  </si>
+  <si>
+    <t>1,3,2,4</t>
+  </si>
+  <si>
+    <t>2,1,3,4</t>
+  </si>
+  <si>
+    <t>4,2,1,3</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan xalqı hansı niyyətlərini bəyan edir? 
+1.Azərbaycan dövlətinin müstəqilliyini, suverenliyini və ərazi bütövlüyünü qorumaq 
+2.Demokratik prinsiplərə əsaslanaraq, xalqın layiqli həyat səviyyəsinin təmin edilməsini 
+3.İnsan və vətəndaşları hüquq və azadlıqlarının təmin olunması 
+4.Konstitusiya çərçivəsində demokratik quruluşa təminat vermək 
+5.Vətəndaş cəmiyyətinin bərqərar edilməsinə nail olmaq</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>1,3,4</t>
+  </si>
+  <si>
+    <t>1,4,5</t>
+  </si>
+  <si>
+    <t>2,4,5</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan xalqı hansı niyyətlərini bəyan edir? 
+1.Xalqın iradəsinin ifadəsi kimi, qanunların aliliyini təmin edən hüquqi, dünyəvi dövlət qurmaq 
+2.Ədalətli iqtisadi və sosial qaydalara uyğun olaraq , hamının layiqli həyat səviyyəsini təmin etmək 
+3.Konstitusiya çərçivəsində unitar respublika yaratmaq 
+4.Azərbaycan Respublikasının beynəlxalq müqavilələrə qoşulmasını təmin etmək 
+5.Ümumbəşəri dəyərlərə sadiq olaraq, bütün dünya xalqları ilə dostluq, sülh və əminamanlıq şəraitində yaşamaq və bu məqsədlə qarşılıqlı fəaliyyət göstərmək</t>
+  </si>
+  <si>
+    <t>1,3,5</t>
+  </si>
+  <si>
+    <t>1,2,5</t>
+  </si>
+  <si>
+    <t>1,4.5</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasıının Konstitusiyası hansı yolla qəbul edilir?</t>
+  </si>
+  <si>
+    <t>Ümumxalq səsverməsi-referendum yolu ilə</t>
+  </si>
+  <si>
+    <t>Milli Məclis Konstitusiya Qanunu ilə</t>
+  </si>
+  <si>
+    <t>Prezidentin təklifinə uyğun olaraq Milli Məclis, Qanunla</t>
+  </si>
+  <si>
+    <t>Heç biri</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan Respublikasında dövlət hakimiyyətinin yeganə mənbəyi kimdir?</t>
+  </si>
+  <si>
+    <t>Azərbaycan xalqı</t>
+  </si>
+  <si>
+    <t>Bütün türk xalqları</t>
+  </si>
+  <si>
+    <t>Vətəndaşlığı və ya vətəndaşlığı olmayanlar</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan xalqı ibarətdir: (Tam və doğru cavab)</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikası ərazisində və ondan kənarda yaşayan, Azərbaycan dövlətinə və onun qanunlarına tabe sayılan Azərbaycan Respublikası vətəndaşlarından və ya vətəndaşı olmayan şəxslərdən ibarətdir</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikası ərazisində və ondan kənarda yaşayan, Azərbaycan dövlətinə və onun qanunlarına tabe sayılan Azərbaycan Respublikası vətəndaşlarından ibarətdir.</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikası ərazisində yaşayan, Azərbaycan dövlətinə və onun qanunlarına tabe sayılan Azərbaycan Respublikası vətəndaşlarından ibarətdir.</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikası ərazisində və ondan kənarda yaşayan, Azərbaycan dövlətinə tabe sayılan Azərbaycan Respublikası vətəndaşlarından ibarətdir.</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan xalqının suveren hüququdur:</t>
+  </si>
+  <si>
+    <t>İnsan və vətəndaşları hüquq və azadlıqlarının təmin olunmasını həyata keçirmək</t>
+  </si>
+  <si>
+    <t>İnsan və vətəndaşların layiqli həyat səviyəsini təmin etmək</t>
+  </si>
+  <si>
+    <t>Sərbəst və müstəqil öz müqəddəratını həll etmək və öz idarəetmə formasını müəyyən etmək</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan xalqı öz suveren hüququnu necə həyata keçirir? (Tam və doğru cavab)</t>
+  </si>
+  <si>
+    <t>Bilavasitə ümumxalq səsverməsi - referendum və ümumi, bərabər və birbaşa seçki hüququ əsasında sərbəst, gizli və şəxsi səsvermə yolu ilə seçilmiş nümayəndələri vasitəsi ilə</t>
+  </si>
+  <si>
+    <t>Bilavasitə ümumxalq səsverməsi və ümumi, bərabər və birbaşa seçki hüququ əsasında sərbəst, gizli və şəxsi səsvermə yolu ilə seçilmiş nümayəndələri vasitəsi ilə</t>
+  </si>
+  <si>
+    <t>Bilavasitə referendum və ümumi, bərabər və birbaşa seçki hüquq</t>
+  </si>
+  <si>
+    <t>Bilavasitə majoritar seçki sistemi vasitəsilə , ümumi, bərabər və birbaşa seçki hüququ əsasında sərbəst, gizli və şəxsi səsvermə yolu ilə seçilmiş nümayəndələri vasitəsi ilə</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq hansı məsələlər referendumla həll edilə bilər? 
+1. Azərbaycan xalqının öz hüquqları ilə bağlı olan məsələlər 
+2. Azərbaycan Respublikası Konstitusiyasının qəbul edilməsi və ona dəyişikliklər edilməsi 
+3. Azərbaycan xalqının öz mənafeləri ilə bağlı olan məsələlər 
+4. Azərbaycan Respublikasının dövlət sərhədlərinin dəyişdirilməsi 
+5. Vergilər və dövlət büdcəsi 
+6. Amnistiya və əfv etmə 
+7. Seçilməsi, təyin edilməsi və ya təsdiq edilməsi müvafiq olaraq qanunvericilik və (və ya) icra hakimiyyəti orqanlarının səlahiyyətlərinə aid edilmiş vəzifəli şəxslərin seçilməsi, təyin edilməsi və ya təsdiq edilməsi</t>
+  </si>
+  <si>
+    <t>5,6,7</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq yalnız referendumla həll oluna bilən məsələlərə aiddir:
+1.	Azərbaycan xalqının öz hüquqları ilə bağlı olan məsələlər
+2.	Azərbaycan Respublikası Konstitusiyasının qəbul edilməsi və ona dəyişikliklər edilməsi
+3.	Azərbaycan xalqının öz mənafeləri ilə bağlı olan məsələlər
+4.	Azərbaycan Respublikasının dövlət sərhədlərinin dəyişdirilməsi
+5.	Vergilər və dövlət büdcəsi
+6.	Amnistiya və əfv etmə
+7.	Seçilməsi, təyin edilməsi və ya təsdiq edilməsi müvafiq olaraq qanunvericilik və (və ya) icra hakimiyyəti orqanlarının səlahiyyətlərinə aid edilmiş vəzifəli şəxslərin seçilməsi, təyin edilməsi və ya təsdiq edilməsi</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq hansı məsələlər üzrə referendum keçirilə bilməz?
+1.	Azərbaycan xalqı öz hüquqları ilə bağlı olan məsələlər
+2.	Azərbaycan Respublikası Konstitusiyasının qəbul edilməsi və ona dəyişikliklər edilməsi
+3.	Azərbaycan xalqı öz mənafeləri ilə bağlı olan məsələlər 4.Azərbaycan Respublikasının dövlət sərhədlərinin dəyişdirilməsi
+5.	Vergilər və dövlət büdcəsi
+6.	Amnistiya və əfv etmə
+7.	Seçilməsi, təyin edilməsi və ya təsdiq edilməsi müvafiq olaraq qanunvericilik və (və ya)icra hakimiyyəti orqanlarının səlahiyyətlərinə aid edilmiş vəzifəli şəxslərin seçilməsi, təyin edilməsi və ya təsdiq edilməsi</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq kimlərin xalqın adından danışmaq və xalqın adından müraciət etmək hüququ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>yoxdur</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>Prezident</t>
+  </si>
+  <si>
+    <t>Deputatlar</t>
+  </si>
+  <si>
+    <t>Prezident və deputatların</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.	Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq doğru olan bəndi müəyyən edin : (Tam və doğru cavab)
+1.	Azərbaycan xalqı vahiddir.
+2.	Azərbaycan xalqının vahidliyi Azərbaycan dövlətinin təməlini təşkil edir. 3.Azərbaycan Respublikası Azərbaycanda yaşayan Azərbaycan Respublikası vətəndaşlarının ümumi və bölünməz vətənidir.
+4.	Azərbaycan xalqının heç bir hissəsi, sosial qrup, təşkilat və ya heç bir şəxs hakimiyyətin həyata keçirilməsi səlahiyyətini mənimsəyə bilməz.
+Hakimiyyətin mənimsənilməsi xalqa qarşı ən ağır cinayətdir. </t>
+  </si>
+  <si>
+    <t>1,2,4,5</t>
+  </si>
+  <si>
+    <t>2,3,4,5</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan dövləti:																																																						
+1. Demokratik Respublikadır.																																																						
+2. İslami Respublikadır.																																																						
+3. Hüquqi Respublikadır.																																																						
+4. Dünyəvi Respublikadır.																																																						
+5. Federativ Respublikadır.																																																						</t>
+  </si>
+  <si>
+    <t>2,3,5</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan Respublikasında dövlət hakimiyyəti daxili məsələlərdə ............ xarici məsələlərdə isə ........... məhdudlaşır:</t>
+  </si>
+  <si>
+    <t>Yalnız hüquqla, yalnız Azərbaycan Respublikasının tərəfdar çıxdığı beynəlxalq müqavilələrdən irəli gələn müddəalarla</t>
+  </si>
+  <si>
+    <t>Yalnız qanunla, yalnız Azərbaycan Respublikasının tərəfdar çıxdığı beynəlxalq müqavilələrdən irəli gələn müddəalarla</t>
+  </si>
+  <si>
+    <t>Yalnız qanunla, yalnız beynəlxalq müqavilələrdən irəli gələn müddəalarla</t>
+  </si>
+  <si>
+    <t>Yalnız konstitusiya qanunu ilə, yalnız Azərbaycan Respublikasının tərəfdar çıxdığı beynəlxalq müqavilələrdən irəli gələn müddəalarla</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan Respublikasında dövlət hakimiyyəti təşkil edilir:</t>
+  </si>
+  <si>
+    <t>Hakimiyyətlərin bölünməsi prinsipi əsasında</t>
+  </si>
+  <si>
+    <t>Dövlətin bölünməsi prinsipi əsasında</t>
+  </si>
+  <si>
+    <t>Qanunla müəyyən olunmuş qaydada</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq doğru olan bəndi
+müyyən edin:
+1.Qanunvericilik hakimiyyətini Azərbaycan Respublikasının Milli Məclisi həyata keçirir
+2.İcra hakimiyyəti Azərbaycan Respublikasının Nazirlər Kabinetinə mənsubdur
+3.Məhkəmə hakimiyyətini Azərbaycan Respublikasının məhkəmələri həyata keçirir
+4.Qanuna uyğun olaraq qanunvericilik, icra və məhkəmə hakimiyyətləri qarşılıqlı
+fəaliyyət göstərir və öz səlahiyyətləri çərçivəsində müstəqildirlər</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan
+Respublikasının Prezidenti ............təcəssüm etdirir:</t>
+  </si>
+  <si>
+    <t>Azərbaycan xalqının bütövlüyünü</t>
+  </si>
+  <si>
+    <t>Demokratik prinsipləri</t>
+  </si>
+  <si>
+    <t>İnsan və vətəndaş hüquq və azadlıqlarını</t>
+  </si>
+  <si>
+    <t>Azərbaycan xalqının vahidliyini</t>
+  </si>
+  <si>
+    <t>7.	Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq doğru olan bəndi müəyyən edin:
+1.	Azərbaycan dövlətinin başçısı Azərbaycan Respublikasının Prezidentidir. 
+2.Azərbaycan Respublikasının Prezidenti ölkənin daxilində və xarici münasibətlərdə Azərbaycan dövlətini təmsil edir.
+3.	Azərbaycan dövlətçiliyinin varisliyini təmin edir.
+4.	Azərbaycan Respublikasının Prezidenti Azərbaycan dövlətinin suverenliyinin, ərazi bütövlüyünün və Azərbaycan Respublikasının tərəfdar çıxdığı beynəlxalq müqavilələrə riayət olunmasının təminatçısıdır.</t>
+  </si>
+  <si>
+    <t>2,3,4</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan Respublikası Silahlı Qüvvələr yaradır?</t>
+  </si>
+  <si>
+    <t>Ərazi bütövlüyünü genişləndirmək üçün</t>
+  </si>
+  <si>
+    <t>İnsan və vətəndaş hüquq və azadlıqlarını qorumaq üçün</t>
+  </si>
+  <si>
+    <t>Öz təhlükəsizliyini və müdafiəsini təmin etmək məqsədi ilə</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Silahlı Qüvvələr ibarətdir: (Tam və doğru cavab)</t>
+  </si>
+  <si>
+    <t>Azərbaycan Ordusundan və başqa silahlı birləşmələrdən</t>
+  </si>
+  <si>
+    <t>Azərbaycan Ordusundan</t>
+  </si>
+  <si>
+    <t>Azərbaycan Ordusundan və Daxili Qoşunlardan</t>
+  </si>
+  <si>
+    <t>Azərbaycan Ordusundan və Dövlət Sərxəd Xidmətindən</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan Respublikası başqa dövlətlərin müstəqilliyinə qəsd vasitəsi kimi və beynəlxalq münaqişələrin həlli üsulu kimi rədd edir:</t>
+  </si>
+  <si>
+    <t>Münaqişəni</t>
+  </si>
+  <si>
+    <t>Müharibəni</t>
+  </si>
+  <si>
+    <t>Mübarizəni</t>
+  </si>
+  <si>
+    <t>Müdafiəni</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan Respublikası başqa dövlətlərlə münasibətlərini hansı prinsiplər əsasında qurur?</t>
+  </si>
+  <si>
+    <t>Hamılıqla qəbul edilmiş beynəlxalq hüquq normalarında nəzərdə tutulan prinsiplər</t>
+  </si>
+  <si>
+    <t>Beynəlxalq müqavilələrə əsasən</t>
+  </si>
+  <si>
+    <t>Konstitusiyaya əsasən</t>
+  </si>
+  <si>
+    <t>Tərəfdar çıxdığımız beynəlxalq müqavilələrə əsasən</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq doğru olan bəndi seçin:
+1. Azərbaycan Respublikasının ərazisi vahiddir, toxunulmazdır və bölünməzdir.
+2. Azərbaycan Respublikasının daxili suları, Xəzər dənizinin (gölünün) Azərbaycan Respublikasına mənsub olan bölməsi, Azərbaycan Respublikasının üzərindəki hava məkanı Azərbaycan Respublikası ərazisinin tərkib hissəsidir.
+3. Azərbaycan Respublikasının ərazisi qanunla müəyyən olunmuş qaydada özgəninkiləşdirilə bilər
+4. Azərbaycan Respublikası öz ərazisinin heç bir hissəsini heç bir şəkildə kimsəyə vermir</t>
+  </si>
+  <si>
+    <t>1,2,4</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq hansı halda Azərbaycan xalqının iradəsi əsasında dövlət sərhədləri dəyişdirilə bilər?</t>
+  </si>
+  <si>
+    <t>Yalnız Azərbaycan Respublikası Milli Məclisinin qərarı ilə Azərbaycanın bütün əhalisi arasında referendum keçirmək yolu ilə</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikası Milli Məclisinin qərarı və ya Prezidentin fərmanı ilə Azərbaycanın bütün əhalisi arasında referendum keçirmək yolu ilə</t>
+  </si>
+  <si>
+    <t>Yalnız Azərbaycan Respublikası Prezidentinin fərnmanı ilə Azərbaycanın bütün əhalisi arasında referendum keçirmək yolu ilə</t>
+  </si>
+  <si>
+    <t>Yalnız Azərbaycan Respublikası Milli Məclisinin qərarı ilə Azərbaycanın bütün əhalisi arasında ümumxalq səsverməsi keçirmək yolu ilə</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq dövlətin ali məqsədi nədir?</t>
+  </si>
+  <si>
+    <t>Ümumbəşəri dəyərlərə sadiq olaraq, bütün dünya xalqları ilə dostluq, sülh və əmin-amanlıq şəraitində yaşamaq və bu məqsədlə qarşılıqlı fəaliyyət göstərmək</t>
+  </si>
+  <si>
+    <t>Azərbaycan dövlətinin müstəqilliyini, suverenliyini və ərazi bütövlüyünü qorumaq</t>
+  </si>
+  <si>
+    <t>Xalqın iradəsinin ifadəsi kimi, qanunların aliliyini təmin edən hüquqi, dünyəvi dövlət qurmaq</t>
+  </si>
+  <si>
+    <t>İnsan və vətəndaş hüquqlarının və azadlıqlarının, Azərbaycan Respublikasının vətəndaşlarına layiqli həyat səviyyəsinin təmin edilməsi</t>
+  </si>
+  <si>
+    <t>Konstitusiyada sadalanan insan və vətəndaş hüquqları və azadlıqları tətbiq edilir:</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının tərəfdar çıxdığı beynəlxalq müqavilələrə uyğun</t>
+  </si>
+  <si>
+    <t>Konstitusiyaya uyğun</t>
+  </si>
+  <si>
+    <t>Qanuna uyğun</t>
+  </si>
+  <si>
+    <t>Konstitusiya qanununa uyğun</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan Respublikasında mülkiyyət toxunulmazdır və kim tərəfindən müdafiə olunur?</t>
+  </si>
+  <si>
+    <t>Məhkəmə</t>
+  </si>
+  <si>
+    <t>Dövlət</t>
+  </si>
+  <si>
+    <t>Milli Məclis</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq mülkiyyət .......... növündə ola bilər:</t>
+  </si>
+  <si>
+    <t>Dövlət mülkiyyəti, xüsusi mülkiyyət və bələdiyyə mülkiyyəti</t>
+  </si>
+  <si>
+    <t>Torpaq, xüsusi, şəxsi</t>
+  </si>
+  <si>
+    <t>Dövlət, ümumi, xüsusi</t>
+  </si>
+  <si>
+    <t>Torpaq, dövlət, bələdiyyə, xüsusi</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq mülkiyyətdən ........
+əleyhinə istifadə edilə bilməz:
+1. İnsan və vətəndaş hüquqları və azadlıqları 
+2. Cəmiyyətin və dövlətin mənafeləri
+3. Fiziki və hüquqi şəxslərin əmlakı
+4. Şəxsiyyətin ləyaqəti əleyhinə</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq təbii ehtiyatlar kimə mənsubdur:</t>
+  </si>
+  <si>
+    <t>Hər hansı fiziki və ya hüquqi şəxslərin hüquqlarına və mənafelərinə xələl gətirmədən Azərbaycan Respublikasına</t>
+  </si>
+  <si>
+    <t>Xalqa</t>
+  </si>
+  <si>
+    <t>Dövlətə</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Azərbaycan Respublikasında iqtisadiyyatın inkişafı nəyə xidmət edir?</t>
+  </si>
+  <si>
+    <t>Xüsusi mülkiyyət növünə əsaslanaraq xalqın rifahının yüksəldilməsinə</t>
+  </si>
+  <si>
+    <t>Bələdiyyə mülkiyyət növünə əsaslanaraq xalqın rifahının yüksəldilməsinə</t>
+  </si>
+  <si>
+    <t>Dövlət mülkiyyət növünə əsaslanaraq xalqın rifahının yüksəldilməsinə</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq kim bazar münasibətləri əsasında sosial yönümlü iqtisadiyyatın inkişafına şərait yaradır, azad sahibkarlığa təminat verir, iqtisadi münasibətlərdə inhisarçılığa və haqsız rəqabətə yol vermir:</t>
+  </si>
+  <si>
+    <t>Azərbaycan dövləti</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq kim xalqın və hər bir vətəndaşın rifahının yüksəldilməsi, onun sosial müdafiəsi və layiqli həyat səviyyəsi qayğısına qalır:</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq kim mədəniyyətin, təhsilin, səhiyyənin, elmin, incəsənətin inkişafına yardım göstərir, ölkənin təbiətini, xalqın tarixi, maddi və mənəvi irsini qoruyur:</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq düzgün olan bəndi müəyyən edin:
+1.Cəmiyyətin əsas özəyi kimi ailə dövlətin xüsusi himayəsindədir.
+2.Uşaqlara qayğı göstərmək və onları tərbiyə etmək valideynlərin həm hüququ həm də borcudur. Bu hüququn və borcun yerinə yetirilməsinə dövlət nəzarət edir.
+3.Valideynləri və ya qəyyumları olmayan, valideyn qayğısından məhrum olan uşaqlar dövlətin himayəsindədirlər.
+4.Uşaqları onların həyatına, sağlamlığına və ya mənəviyyatına təhlükə törədə bilən fəaliyyətə cəlb etmək qnunla müəyyən olunmuş hallarda mümkündür
+5.15 yaşına çatmamış uşaqlar işə götürülə bilməzlər.
+6.Uşaq hüquqlarının həyata keçirilməsinə dövlət nəzarət edir.</t>
+  </si>
+  <si>
+    <t>1,3,4,5,6</t>
+  </si>
+  <si>
+    <t>1,2,3,5,6</t>
+  </si>
+  <si>
+    <t>2,3,4,5,6</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq hansı dinlərin (dini cərəyanların) yayılması və təbliği qadağandır?</t>
+  </si>
+  <si>
+    <t>Fərqli dini ayinlərin keçrilməsini təmin edən</t>
+  </si>
+  <si>
+    <t>Kişi və qadına eyni hüquq verməyən</t>
+  </si>
+  <si>
+    <t>İnsan ləyaqətini alçaldan və ya insanpərvərlik prinsiplərinə zidd olan</t>
+  </si>
+  <si>
+    <t>Qanunvericilikdə belə bir hal nəzərdə tutulmayıb</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq Dövlət təhsil sistemi hansı xarakter daşıyır?</t>
+  </si>
+  <si>
+    <t>Dünyəvi</t>
+  </si>
+  <si>
+    <t>İcbari</t>
+  </si>
+  <si>
+    <t>Mimimum</t>
+  </si>
+  <si>
+    <t>Maksimum</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq doğru olan bəndi müəyyən edin:
+1.Azərbaycan Respublikasının pul vahidi manatdır.
+2.Pul nişanlarının tədavülə buraxılması və tədavüldən çıxarılması hüququ Mərkəzi Bank və Beynəlxalq Banka mənsubdur.
+3.Azərbaycan Respublikasının Mərkəzi Bankı dövlətin müstəsna mülkiyyətindədir. 
+4.Azərbaycan Respublikasının ərazisində manatdan başqa pul vahidlərinin ödəniş vasitəsi kimi işlədilməsi qanunla müəyyən olunmuşhallarda mümkündür</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq hansı borclar Azərbaycan Respublikası tərəfindən öhdəlik kimi qəbul edilə və ödənilə bilməz?</t>
+  </si>
+  <si>
+    <t>Yalnız Azərbaycan dövlətinə qarşı qiyama kömək məqsədilə alınmış</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yalnız Azərbaycan dövlətinə qarşı dövlət çevrilişinə kömək məqsədi ilə alınmış </t>
+  </si>
+  <si>
+    <t>Azərbaycan dövlətinə qarşı qiyama və dövlət çevrilişinə kömək məqsədi ilə alınmış</t>
+  </si>
+  <si>
+    <t>Azərbaycan dövlətinə qarşı tətilə, qiyama və dövlət çevrilişinə kömək məqsədi ilə alınmış</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq düzgün olmayan bəndi müəyyən edin:</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının dövlət dili Azərbaycan dilidir</t>
+  </si>
+  <si>
+    <t>Dövlət dilini bilmək hər bir Azərbaycan Respublikası vatəndaşının borcudur.</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikası Azərbaycan dilinin inkişafını təmin edir.</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikası əhalinin danışdığı başqa dillərin sərbəst işlədilməsini və inkişafını təmin edir.</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq düzgün olan bənd müəyyən edin:
+1.Azərbaycan Respublikasının dövlət rəmzləri Azərbaycan Respublikasının Dövlət bayrağı, Azərbaycan Respublikasının Dövlət gerbi və Azərbaycan Respublikasının Dövlət himnidir.
+2.Azərbaycan Respublikasının Dövlət bayrağı bərabər enli üç üfüqi zolaqdan ibarətdir.Yuxarı zolaq göy, orta zolaq qırmızı, aşağı zolaq yaşıl rəngdədir və qırmızı zolağın ortasında bayrağın hər iki üzündə ağ rəngli aypara ilə səkkizguşəli ulduz təsvir edilmişdir.
+3.Bayrağın uzunluğunun eninə nisbəti 1:2-dir.
+4.Azərbaycan Respublikası Dövlət bayrağının və Azərbaycan Respublikası Dövlət gerbinin təsviri, Azərbaycan Respublikası Dövlət himninin musiqisi və mətni Konstitusiya qanunu ilə müəyyən edilir.</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq “İnsan ləyaqəti qorunur və ona hörmət edilir”. Göstərilən müddəa hansı maddəyə uyğundur?</t>
+  </si>
+  <si>
+    <t>İnsan və vətəndaş hüquqlarının və azadlıqlarının əsas prinsipi</t>
+  </si>
+  <si>
+    <t>Bərabərlik hüququ</t>
+  </si>
+  <si>
+    <t>İnsan və vətəndaş hüquqlarının müdafiəsi</t>
+  </si>
+  <si>
+    <t>şəxsi toxunulmazlıq hüququ</t>
+  </si>
+  <si>
+    <t>Azərbaycan Respublikasının Konstitusiyasına uyğun olaraq kimlərin doğulduğu andan toxunulmaz, pozulmaz və ayrılmaz hüquqları və azadlıqları vardır?</t>
+  </si>
+  <si>
+    <t>Yalnız hər bir vətənaşın</t>
+  </si>
+  <si>
+    <t>Hər kəsin</t>
+  </si>
+  <si>
+    <t>Hər bir şəxsin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Cambria"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Cambria"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -141,8 +829,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -457,7 +1159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -503,105 +1205,1610 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2">
-        <v>1991</v>
-      </c>
-      <c r="E2">
-        <v>1995</v>
-      </c>
-      <c r="F2">
-        <v>2002</v>
-      </c>
-      <c r="G2">
-        <v>2009</v>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="12.75" customHeight="1">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="12.75" customHeight="1">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="12" customHeight="1">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19">
+        <v>1.3</v>
+      </c>
+      <c r="E19">
+        <v>2.4</v>
+      </c>
+      <c r="F19" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="12" customHeight="1">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20">
+        <v>1.3</v>
+      </c>
+      <c r="E20">
+        <v>2.4</v>
+      </c>
+      <c r="F20" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" customHeight="1">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21">
+        <v>1.3</v>
+      </c>
+      <c r="E21">
+        <v>2.4</v>
+      </c>
+      <c r="F21" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" t="s">
+        <v>45</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G25" t="s">
+        <v>99</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" t="s">
+        <v>43</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D27">
+        <v>1.2</v>
+      </c>
+      <c r="E27">
+        <v>1.3</v>
+      </c>
+      <c r="F27">
+        <v>2.4</v>
+      </c>
+      <c r="G27" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="12" customHeight="1">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" t="s">
+        <v>108</v>
+      </c>
+      <c r="G28" t="s">
+        <v>109</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="12" customHeight="1">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" t="s">
+        <v>111</v>
+      </c>
+      <c r="F29" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15" customHeight="1">
+      <c r="A40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="12.75" customHeight="1">
+      <c r="A49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D49" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="E49" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F49" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="H50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="H51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="12" customHeight="1">
+      <c r="A52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E52" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="B55" s="1"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="B56" s="1"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="B57" s="1"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="B58" s="1"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="B59" s="1"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="B60" s="1"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="B61" s="1"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="B62" s="1"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="B63" s="1"/>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="B64" s="1"/>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="1"/>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="1"/>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="1"/>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="1"/>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="1"/>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="1"/>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="1"/>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="1"/>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="1"/>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="1"/>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="1"/>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="1"/>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="1"/>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="1"/>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="1"/>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="1"/>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="1"/>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="1"/>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="1"/>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="1"/>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="1"/>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="1"/>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="1"/>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" s="1"/>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" s="1"/>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" s="1"/>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91" s="1"/>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92" s="1"/>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93" s="1"/>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="1"/>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" s="1"/>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="1"/>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="1"/>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" s="1"/>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" s="1"/>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="1"/>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" s="1"/>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102" s="1"/>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103" s="1"/>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" s="1"/>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105" s="1"/>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106" s="1"/>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" s="1"/>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108" s="1"/>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" s="1"/>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110" s="1"/>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111" s="1"/>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112" s="1"/>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113" s="1"/>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114" s="1"/>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115" s="1"/>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116" s="1"/>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117" s="1"/>
+    </row>
+    <row r="118" spans="2:2">
+      <c r="B118" s="1"/>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119" s="1"/>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120" s="1"/>
+    </row>
+    <row r="121" spans="2:2">
+      <c r="B121" s="1"/>
+    </row>
+    <row r="122" spans="2:2">
+      <c r="B122" s="1"/>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123" s="1"/>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124" s="1"/>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125" s="1"/>
+    </row>
+    <row r="126" spans="2:2">
+      <c r="B126" s="1"/>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127" s="1"/>
+    </row>
+    <row r="128" spans="2:2">
+      <c r="B128" s="1"/>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129" s="1"/>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130" s="1"/>
+    </row>
+    <row r="131" spans="2:2">
+      <c r="B131" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
